--- a/DxI_CODES.xlsx
+++ b/DxI_CODES.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>AFP</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>CK-MB</t>
+  </si>
+  <si>
+    <t>GI19-9Ag</t>
   </si>
 </sst>
 </file>
@@ -996,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1447,6 +1450,14 @@
         <v>1271</v>
       </c>
     </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
